--- a/output/pdf_financials_xlsx/HANS.xlsx
+++ b/output/pdf_financials_xlsx/HANS.xlsx
@@ -3344,19 +3344,19 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.10107</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.382483</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.424891</v>
+        <v>0.663945</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.518034</v>
+        <v>1.084996</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.563659</v>
+        <v>1.363577</v>
       </c>
     </row>
     <row r="93">
@@ -3652,28 +3652,28 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.049654</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.049654</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.055054</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.029417</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.02349</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.026104</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.151921</v>
       </c>
     </row>
     <row r="104">
@@ -3745,28 +3745,28 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.049654</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.010126</v>
+        <v>0.05978</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.109223</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.874341</v>
+        <v>0.819287</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.156094</v>
+        <v>0.185511</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.224882</v>
+        <v>-0.201392</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.460911</v>
+        <v>0.434807</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.208479</v>
+        <v>0.056558</v>
       </c>
     </row>
     <row r="107">
@@ -5544,7 +5544,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -6154,7 +6158,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -6980,7 +6988,11 @@
           <t>Warrants reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7250,7 +7262,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.049654</v>
       </c>
@@ -7758,7 +7774,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -8776,7 +8796,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -10094,7 +10118,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>-0.049654</v>
       </c>

--- a/output/pdf_financials_xlsx/HANS.xlsx
+++ b/output/pdf_financials_xlsx/HANS.xlsx
@@ -709,16 +709,16 @@
         <v>4.12561</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.415609</v>
+        <v>1.911079</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.271924</v>
+        <v>0.928095</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.223472</v>
+        <v>0.893503</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.289631</v>
+        <v>1.260605</v>
       </c>
     </row>
     <row r="11">
@@ -762,22 +762,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001157</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000923</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000106</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000731</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1263,22 +1263,22 @@
         <v>-0.02777</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.056568</v>
+        <v>-0.057725</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.509847</v>
+        <v>-2.51077</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.873741</v>
+        <v>-3.873847</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.443229</v>
+        <v>-1.44396</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.682335</v>
+        <v>-0.682343</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.893481</v>
+        <v>-0.893503</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.486825</v>
@@ -1325,22 +1325,22 @@
         <v>-0.02777</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.056568</v>
+        <v>-0.057725</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.509847</v>
+        <v>-2.51077</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.873741</v>
+        <v>-3.873847</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.443229</v>
+        <v>-1.44396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.682335</v>
+        <v>-0.682343</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.893481</v>
+        <v>-0.893503</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.486825</v>
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.098276</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.350972</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.568885</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.766893</v>
@@ -1503,10 +1503,10 @@
         <v>0.166566</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003298</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001575</v>
       </c>
     </row>
     <row r="35">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.098276</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.350972</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.568885</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.766893</v>
@@ -1565,10 +1565,10 @@
         <v>0.166566</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003298</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001575</v>
       </c>
     </row>
     <row r="37">
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.350972</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.568885</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.124804</v>
@@ -1937,10 +1937,10 @@
         <v>0.002147</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.031549</v>
+        <v>0.028251</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.181747</v>
+        <v>0.180172</v>
       </c>
     </row>
     <row r="49">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19228,7 +19228,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">

--- a/output/pdf_financials_xlsx/HANS.xlsx
+++ b/output/pdf_financials_xlsx/HANS.xlsx
@@ -3593,13 +3593,13 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.049654</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.075555</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.172994</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.256059</v>
@@ -3748,13 +3748,13 @@
         <v>-0.049654</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.05978</v>
+        <v>0.109434</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.109223</v>
+        <v>0.033668</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.819287</v>
+        <v>0.646293</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0.185511</v>
@@ -10174,7 +10174,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
